--- a/diseases/d200/2020-2025.xlsx
+++ b/diseases/d200/2020-2025.xlsx
@@ -1009,7 +1009,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6575,7 +6575,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8271,7 +8271,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -10206,7 +10206,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10445,7 +10445,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11090,7 +11090,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11735,7 +11735,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -12141,7 +12141,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12380,7 +12380,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -12786,7 +12786,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -13025,7 +13025,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13837,7 +13837,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14076,7 +14076,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14482,7 +14482,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14721,7 +14721,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15127,7 +15127,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15366,7 +15366,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15772,7 +15772,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -16011,7 +16011,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16417,7 +16417,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16656,7 +16656,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -17062,7 +17062,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17707,7 +17707,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17946,7 +17946,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -18352,7 +18352,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18591,7 +18591,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18997,7 +18997,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -19236,7 +19236,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19642,7 +19642,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19881,7 +19881,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -20287,7 +20287,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20526,7 +20526,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -20932,7 +20932,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -21338,7 +21338,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -21744,7 +21744,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -22150,7 +22150,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -22556,7 +22556,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -22962,7 +22962,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -23368,7 +23368,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -23774,7 +23774,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -24180,7 +24180,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -24586,7 +24586,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24992,7 +24992,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -25398,7 +25398,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -25804,7 +25804,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -26043,7 +26043,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -26449,7 +26449,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -26688,7 +26688,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -27094,7 +27094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -27333,7 +27333,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -27739,7 +27739,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27978,7 +27978,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -28384,7 +28384,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -28623,7 +28623,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -29029,7 +29029,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -29268,7 +29268,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -29674,7 +29674,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -29913,7 +29913,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -30319,7 +30319,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -30558,7 +30558,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -30964,7 +30964,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -31203,7 +31203,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -31609,7 +31609,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -31848,7 +31848,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -32254,7 +32254,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -32493,7 +32493,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -32899,7 +32899,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -33138,7 +33138,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -33950,7 +33950,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -34189,7 +34189,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -34595,7 +34595,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -34834,7 +34834,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -35240,7 +35240,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -35479,7 +35479,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -35885,7 +35885,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -36124,7 +36124,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -36530,7 +36530,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -36769,7 +36769,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -37175,7 +37175,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -37414,7 +37414,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -37820,7 +37820,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -38059,7 +38059,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -38465,7 +38465,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -38871,7 +38871,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -39277,7 +39277,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -39683,7 +39683,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">

--- a/diseases/d200/2020-2025.xlsx
+++ b/diseases/d200/2020-2025.xlsx
@@ -1009,7 +1009,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6575,7 +6575,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7220,7 +7220,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8271,7 +8271,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -10206,7 +10206,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10445,7 +10445,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11090,7 +11090,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11735,7 +11735,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -12141,7 +12141,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12380,7 +12380,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -12786,7 +12786,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -13025,7 +13025,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13837,7 +13837,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14076,7 +14076,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14482,7 +14482,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14721,7 +14721,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15127,7 +15127,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15366,7 +15366,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15772,7 +15772,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -16011,7 +16011,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16417,7 +16417,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16656,7 +16656,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -17062,7 +17062,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17707,7 +17707,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17946,7 +17946,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -18352,7 +18352,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18591,7 +18591,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18997,7 +18997,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -19236,7 +19236,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19642,7 +19642,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19881,7 +19881,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -20287,7 +20287,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20526,7 +20526,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -20932,7 +20932,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -21338,7 +21338,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -21744,7 +21744,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -22150,7 +22150,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -22556,7 +22556,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -22962,7 +22962,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -23368,7 +23368,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -23774,7 +23774,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -24180,7 +24180,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -24586,7 +24586,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24992,7 +24992,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -25398,7 +25398,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -25804,7 +25804,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -26043,7 +26043,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -26449,7 +26449,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -26688,7 +26688,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -27094,7 +27094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -27333,7 +27333,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -27739,7 +27739,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27978,7 +27978,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -28384,7 +28384,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -28623,7 +28623,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -29029,7 +29029,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -29268,7 +29268,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -29674,7 +29674,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -29913,7 +29913,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -30319,7 +30319,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -30558,7 +30558,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -30964,7 +30964,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -31203,7 +31203,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -31609,7 +31609,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -31848,7 +31848,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -32254,7 +32254,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -32493,7 +32493,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -32899,7 +32899,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -33138,7 +33138,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -33950,7 +33950,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -34189,7 +34189,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -34595,7 +34595,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -34834,7 +34834,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -35240,7 +35240,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -35479,7 +35479,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -35885,7 +35885,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -36124,7 +36124,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -36530,7 +36530,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -36769,7 +36769,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -37175,7 +37175,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -37414,7 +37414,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -37820,7 +37820,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -38059,7 +38059,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -38465,7 +38465,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -38871,7 +38871,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -39277,7 +39277,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -39683,7 +39683,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">

--- a/diseases/d200/2020-2025.xlsx
+++ b/diseases/d200/2020-2025.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>78</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.03738123505372121</v>
       </c>
@@ -1410,9 +1407,6 @@
       <c r="O5" t="n">
         <v>52</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.02492082336914747</v>
       </c>
@@ -2055,9 +2049,6 @@
       <c r="O8" t="n">
         <v>127</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.06086431861311017</v>
       </c>
@@ -2700,9 +2691,6 @@
       <c r="O11" t="n">
         <v>5</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0.00239623301626418</v>
       </c>
@@ -3345,9 +3333,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -3751,9 +3736,6 @@
       <c r="O16" t="n">
         <v>10</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.00479246603252836</v>
       </c>
@@ -4396,9 +4378,6 @@
       <c r="O19" t="n">
         <v>2</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0.0009584932065056721</v>
       </c>
@@ -5041,9 +5020,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -5447,9 +5423,6 @@
       <c r="O24" t="n">
         <v>12</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.005750959239034032</v>
       </c>
@@ -6092,9 +6065,6 @@
       <c r="O27" t="n">
         <v>1</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0.000479246603252836</v>
       </c>
@@ -6737,9 +6707,6 @@
       <c r="O30" t="n">
         <v>3</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.001437739809758508</v>
       </c>
@@ -7382,9 +7349,6 @@
       <c r="O33" t="n">
         <v>1</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.0004772124061061923</v>
       </c>
@@ -8027,9 +7991,6 @@
       <c r="O36" t="n">
         <v>2</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.0009544248122123846</v>
       </c>
@@ -8672,9 +8633,6 @@
       <c r="O39" t="n">
         <v>9</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.004294911654955731</v>
       </c>
@@ -9317,9 +9275,6 @@
       <c r="O42" t="n">
         <v>3</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.001431637218318577</v>
       </c>
@@ -9962,9 +9917,6 @@
       <c r="O45" t="n">
         <v>21</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.01002146052823004</v>
       </c>
@@ -10607,9 +10559,6 @@
       <c r="O48" t="n">
         <v>5</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.002386062030530962</v>
       </c>
@@ -11252,9 +11201,6 @@
       <c r="O51" t="n">
         <v>6</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.002863274436637154</v>
       </c>
@@ -11897,9 +11843,6 @@
       <c r="O54" t="n">
         <v>9</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.004294911654955731</v>
       </c>
@@ -12542,9 +12485,6 @@
       <c r="O57" t="n">
         <v>10</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.004772124061061924</v>
       </c>
@@ -13187,9 +13127,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -13593,9 +13530,6 @@
       <c r="O62" t="n">
         <v>4</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.001901986684291078</v>
       </c>
@@ -14238,9 +14172,6 @@
       <c r="O65" t="n">
         <v>19</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.009034436750382619</v>
       </c>
@@ -14883,9 +14814,6 @@
       <c r="O68" t="n">
         <v>8</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.003803973368582155</v>
       </c>
@@ -15528,9 +15456,6 @@
       <c r="O71" t="n">
         <v>60</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.02852980026436617</v>
       </c>
@@ -16173,9 +16098,6 @@
       <c r="O74" t="n">
         <v>79</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.03756423701474879</v>
       </c>
@@ -16818,9 +16740,6 @@
       <c r="O77" t="n">
         <v>7</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.003328476697509386</v>
       </c>
@@ -17463,9 +17382,6 @@
       <c r="O80" t="n">
         <v>132</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.06276556058160557</v>
       </c>
@@ -18108,9 +18024,6 @@
       <c r="O83" t="n">
         <v>390</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.1854437017183801</v>
       </c>
@@ -18753,9 +18666,6 @@
       <c r="O86" t="n">
         <v>489</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.2325178721545842</v>
       </c>
@@ -19398,9 +19308,6 @@
       <c r="O89" t="n">
         <v>581</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0.2762635658932791</v>
       </c>
@@ -20043,9 +19950,6 @@
       <c r="O92" t="n">
         <v>176</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.08368741410880741</v>
       </c>
@@ -20688,9 +20592,6 @@
       <c r="O95" t="n">
         <v>8</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.003788942113579612</v>
       </c>
@@ -21094,9 +20995,6 @@
       <c r="O97" t="n">
         <v>15</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0.007104266462961772</v>
       </c>
@@ -21500,9 +21398,6 @@
       <c r="O99" t="n">
         <v>37</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.0175238572753057</v>
       </c>
@@ -21906,9 +21801,6 @@
       <c r="O101" t="n">
         <v>79</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.03741580337159867</v>
       </c>
@@ -22312,9 +22204,6 @@
       <c r="O103" t="n">
         <v>141</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.06678010475184065</v>
       </c>
@@ -22718,9 +22607,6 @@
       <c r="O105" t="n">
         <v>167</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.07909416662097439</v>
       </c>
@@ -23124,9 +23010,6 @@
       <c r="O107" t="n">
         <v>19</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.008998737519751578</v>
       </c>
@@ -23530,9 +23413,6 @@
       <c r="O109" t="n">
         <v>284</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.1345074450320762</v>
       </c>
@@ -23936,9 +23816,6 @@
       <c r="O111" t="n">
         <v>414</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.1960777543777449</v>
       </c>
@@ -24342,9 +24219,6 @@
       <c r="O113" t="n">
         <v>349</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.1652925997049106</v>
       </c>
@@ -24748,9 +24622,6 @@
       <c r="O115" t="n">
         <v>438</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.2074445807184837</v>
       </c>
@@ -25154,9 +25025,6 @@
       <c r="O117" t="n">
         <v>151</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.07151628239381516</v>
       </c>
@@ -25560,9 +25428,6 @@
       <c r="O119" t="n">
         <v>16</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.007547220594859333</v>
       </c>
@@ -26205,9 +26070,6 @@
       <c r="O122" t="n">
         <v>5</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.002358506435893542</v>
       </c>
@@ -26850,9 +26712,6 @@
       <c r="O125" t="n">
         <v>57</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.02688697336918637</v>
       </c>
@@ -27495,9 +27354,6 @@
       <c r="O128" t="n">
         <v>105</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.04952863515376438</v>
       </c>
@@ -28140,9 +27996,6 @@
       <c r="O131" t="n">
         <v>123</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.05801925832298113</v>
       </c>
@@ -28785,9 +28638,6 @@
       <c r="O134" t="n">
         <v>110</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.05188714158965792</v>
       </c>
@@ -29430,9 +29280,6 @@
       <c r="O137" t="n">
         <v>19</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.008962324456395459</v>
       </c>
@@ -30075,9 +29922,6 @@
       <c r="O140" t="n">
         <v>354</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.1669822556612627</v>
       </c>
@@ -30720,9 +30564,6 @@
       <c r="O143" t="n">
         <v>316</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.1490576067484718</v>
       </c>
@@ -31365,9 +31206,6 @@
       <c r="O146" t="n">
         <v>586</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.2764169542867231</v>
       </c>
@@ -32010,9 +31848,6 @@
       <c r="O149" t="n">
         <v>160</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.07547220594859333</v>
       </c>
@@ -32655,9 +32490,6 @@
       <c r="O152" t="n">
         <v>91</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0.04292481713326245</v>
       </c>
@@ -33300,9 +33132,6 @@
       <c r="O155" t="n">
         <v>2</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.0009397948394972558</v>
       </c>
@@ -33706,9 +33535,6 @@
       <c r="O157" t="n">
         <v>1</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0.0004698974197486279</v>
       </c>
@@ -34351,9 +34177,6 @@
       <c r="O160" t="n">
         <v>74</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.03477240906139847</v>
       </c>
@@ -34996,9 +34819,6 @@
       <c r="O163" t="n">
         <v>104</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.0488693316538573</v>
       </c>
@@ -35641,9 +35461,6 @@
       <c r="O166" t="n">
         <v>128</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0.06014686972782437</v>
       </c>
@@ -36286,9 +36103,6 @@
       <c r="O169" t="n">
         <v>141</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0.06625553618455654</v>
       </c>
@@ -36931,9 +36745,6 @@
       <c r="O172" t="n">
         <v>25</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0.0117474354937157</v>
       </c>
@@ -37576,9 +37387,6 @@
       <c r="O175" t="n">
         <v>147</v>
       </c>
-      <c r="Q175" t="n">
-        <v>0</v>
-      </c>
       <c r="R175" t="n">
         <v>0.0690749207030483</v>
       </c>
@@ -38221,9 +38029,6 @@
       <c r="O178" t="n">
         <v>352</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0.165403891751517</v>
       </c>
@@ -38627,9 +38432,6 @@
       <c r="O180" t="n">
         <v>500</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0.2349487098743139</v>
       </c>
@@ -39033,9 +38835,6 @@
       <c r="O182" t="n">
         <v>200</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0.09397948394972558</v>
       </c>
@@ -39438,9 +39237,6 @@
       </c>
       <c r="O184" t="n">
         <v>167</v>
-      </c>
-      <c r="Q184" t="n">
-        <v>0</v>
       </c>
       <c r="R184" t="n">
         <v>0.07847286909802086</v>

--- a/diseases/d200/2020-2025.xlsx
+++ b/diseases/d200/2020-2025.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8471,7 +8471,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -11442,7 +11442,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11681,7 +11681,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -12084,7 +12084,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12323,7 +12323,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -12726,7 +12726,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -12965,7 +12965,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13771,7 +13771,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14652,7 +14652,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15055,7 +15055,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15697,7 +15697,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -15936,7 +15936,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16339,7 +16339,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16578,7 +16578,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -16981,7 +16981,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -17220,7 +17220,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17623,7 +17623,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17862,7 +17862,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -18265,7 +18265,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18504,7 +18504,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18907,7 +18907,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -19146,7 +19146,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19549,7 +19549,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19788,7 +19788,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20430,7 +20430,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -20833,7 +20833,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -21236,7 +21236,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -21639,7 +21639,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -22042,7 +22042,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -22445,7 +22445,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -22848,7 +22848,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -23251,7 +23251,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -23654,7 +23654,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -24057,7 +24057,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -24460,7 +24460,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24863,7 +24863,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -25266,7 +25266,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -25669,7 +25669,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -25908,7 +25908,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -26311,7 +26311,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -26550,7 +26550,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -26953,7 +26953,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -27192,7 +27192,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -27595,7 +27595,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27834,7 +27834,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -28237,7 +28237,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -28476,7 +28476,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -28879,7 +28879,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -29118,7 +29118,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -29521,7 +29521,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -29760,7 +29760,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -30163,7 +30163,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -30402,7 +30402,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -30805,7 +30805,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -31044,7 +31044,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -31447,7 +31447,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -31686,7 +31686,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -32089,7 +32089,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -32328,7 +32328,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -32731,7 +32731,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -32970,7 +32970,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -33373,7 +33373,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -33776,7 +33776,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -34015,7 +34015,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -34418,7 +34418,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -34657,7 +34657,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -35060,7 +35060,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -35299,7 +35299,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -35702,7 +35702,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -35941,7 +35941,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -36344,7 +36344,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -36583,7 +36583,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -36986,7 +36986,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -37225,7 +37225,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -37628,7 +37628,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -37867,7 +37867,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -38270,7 +38270,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -38673,7 +38673,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -39076,7 +39076,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -39479,7 +39479,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">

--- a/diseases/d200/2020-2025.xlsx
+++ b/diseases/d200/2020-2025.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8471,7 +8471,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -11442,7 +11442,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11681,7 +11681,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -12084,7 +12084,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12323,7 +12323,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -12726,7 +12726,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -12965,7 +12965,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13771,7 +13771,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14652,7 +14652,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15055,7 +15055,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15697,7 +15697,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -15936,7 +15936,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16339,7 +16339,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16578,7 +16578,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -16981,7 +16981,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -17220,7 +17220,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17623,7 +17623,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17862,7 +17862,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -18265,7 +18265,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18504,7 +18504,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18907,7 +18907,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -19146,7 +19146,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19549,7 +19549,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19788,7 +19788,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20430,7 +20430,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -20833,7 +20833,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -21236,7 +21236,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -21639,7 +21639,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -22042,7 +22042,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -22445,7 +22445,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -22848,7 +22848,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -23251,7 +23251,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -23654,7 +23654,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -24057,7 +24057,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -24460,7 +24460,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24863,7 +24863,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -25266,7 +25266,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -25669,7 +25669,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -25908,7 +25908,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -26311,7 +26311,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -26550,7 +26550,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -26953,7 +26953,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -27192,7 +27192,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -27595,7 +27595,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27834,7 +27834,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -28237,7 +28237,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -28476,7 +28476,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -28879,7 +28879,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -29118,7 +29118,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -29521,7 +29521,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -29760,7 +29760,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -30163,7 +30163,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -30402,7 +30402,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -30805,7 +30805,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -31044,7 +31044,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -31447,7 +31447,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -31686,7 +31686,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -32089,7 +32089,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -32328,7 +32328,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -32731,7 +32731,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -32970,7 +32970,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -33373,7 +33373,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -33776,7 +33776,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -34015,7 +34015,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -34418,7 +34418,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -34657,7 +34657,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -35060,7 +35060,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -35299,7 +35299,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -35702,7 +35702,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -35941,7 +35941,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -36344,7 +36344,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -36583,7 +36583,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -36986,7 +36986,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -37225,7 +37225,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -37628,7 +37628,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -37867,7 +37867,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -38270,7 +38270,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -38673,7 +38673,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -39076,7 +39076,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -39479,7 +39479,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">

--- a/diseases/d200/2020-2025.xlsx
+++ b/diseases/d200/2020-2025.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8471,7 +8471,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -11442,7 +11442,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11681,7 +11681,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -12084,7 +12084,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12323,7 +12323,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -12726,7 +12726,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -12965,7 +12965,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13771,7 +13771,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14652,7 +14652,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15055,7 +15055,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15697,7 +15697,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -15936,7 +15936,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16339,7 +16339,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16578,7 +16578,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -16981,7 +16981,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -17220,7 +17220,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17623,7 +17623,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17862,7 +17862,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -18265,7 +18265,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18504,7 +18504,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18907,7 +18907,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -19146,7 +19146,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19549,7 +19549,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19788,7 +19788,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20430,7 +20430,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -20833,7 +20833,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -21236,7 +21236,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -21639,7 +21639,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -22042,7 +22042,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -22445,7 +22445,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -22848,7 +22848,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -23251,7 +23251,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -23654,7 +23654,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -24057,7 +24057,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -24460,7 +24460,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24863,7 +24863,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -25266,7 +25266,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -25669,7 +25669,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -25908,7 +25908,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -26311,7 +26311,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -26550,7 +26550,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -26953,7 +26953,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -27192,7 +27192,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -27595,7 +27595,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27834,7 +27834,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -28237,7 +28237,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -28476,7 +28476,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -28879,7 +28879,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -29118,7 +29118,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -29521,7 +29521,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -29760,7 +29760,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -30163,7 +30163,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -30402,7 +30402,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -30805,7 +30805,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -31044,7 +31044,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -31447,7 +31447,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -31686,7 +31686,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -32089,7 +32089,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -32328,7 +32328,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -32731,7 +32731,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -32970,7 +32970,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -33373,7 +33373,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -33776,7 +33776,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -34015,7 +34015,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -34418,7 +34418,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -34657,7 +34657,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -35060,7 +35060,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -35299,7 +35299,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -35702,7 +35702,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -35941,7 +35941,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -36344,7 +36344,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -36583,7 +36583,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -36986,7 +36986,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -37225,7 +37225,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -37628,7 +37628,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -37867,7 +37867,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -38270,7 +38270,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -38673,7 +38673,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -39076,7 +39076,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -39479,7 +39479,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">

--- a/diseases/d200/2020-2025.xlsx
+++ b/diseases/d200/2020-2025.xlsx
@@ -1006,7 +1006,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8471,7 +8471,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10397,7 +10397,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11039,7 +11039,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
@@ -11442,7 +11442,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11681,7 +11681,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -12084,7 +12084,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12323,7 +12323,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -12726,7 +12726,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -12965,7 +12965,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -13368,7 +13368,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13771,7 +13771,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14652,7 +14652,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15055,7 +15055,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15697,7 +15697,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -15936,7 +15936,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16339,7 +16339,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16578,7 +16578,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -16981,7 +16981,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -17220,7 +17220,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17623,7 +17623,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17862,7 +17862,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -18265,7 +18265,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18504,7 +18504,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18907,7 +18907,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -19146,7 +19146,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19549,7 +19549,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19788,7 +19788,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -20191,7 +20191,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20430,7 +20430,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -20833,7 +20833,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -21236,7 +21236,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -21639,7 +21639,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -22042,7 +22042,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -22445,7 +22445,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -22848,7 +22848,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -23251,7 +23251,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -23654,7 +23654,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -24057,7 +24057,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -24460,7 +24460,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24863,7 +24863,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -25266,7 +25266,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -25669,7 +25669,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -25908,7 +25908,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -26311,7 +26311,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -26550,7 +26550,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -26953,7 +26953,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -27192,7 +27192,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -27595,7 +27595,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27834,7 +27834,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -28237,7 +28237,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -28476,7 +28476,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -28879,7 +28879,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -29118,7 +29118,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -29521,7 +29521,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -29760,7 +29760,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -30163,7 +30163,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -30402,7 +30402,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -30805,7 +30805,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -31044,7 +31044,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -31447,7 +31447,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -31686,7 +31686,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -32089,7 +32089,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -32328,7 +32328,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -32731,7 +32731,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -32970,7 +32970,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -33373,7 +33373,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -33776,7 +33776,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK158" t="inlineStr">
@@ -34015,7 +34015,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -34418,7 +34418,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -34657,7 +34657,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -35060,7 +35060,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -35299,7 +35299,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -35702,7 +35702,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -35941,7 +35941,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -36344,7 +36344,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
@@ -36583,7 +36583,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -36986,7 +36986,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -37225,7 +37225,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -37628,7 +37628,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK176" t="inlineStr">
@@ -37867,7 +37867,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -38270,7 +38270,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -38673,7 +38673,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -39076,7 +39076,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -39479,7 +39479,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
